--- a/course-design-2/outputs/tables/ch7/39_stage26_1_temporal_split.xlsx
+++ b/course-design-2/outputs/tables/ch7/39_stage26_1_temporal_split.xlsx
@@ -17,7 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Temporal主模型结果" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_SafeF补充对照" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_跨子集重叠审计" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_方法与口径" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_方法与统计范围" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch7/39_stage26_1_temporal_split.xlsx
+++ b/course-design-2/outputs/tables/ch7/39_stage26_1_temporal_split.xlsx
@@ -738,7 +738,6 @@
           <t>业务发布时间（岗位代表记录对应的发布时间），不使用爬取时间</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,7 +750,6 @@
           <t>按业务发布日期排序，最早约 70% → train，随后约 15% → validation，最新约 15% → test；按日期边界切割，同一天不拆分</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -764,7 +762,6 @@
           <t>A+B+C+D+E（不依赖存在时点争议的 F 组）</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -777,7 +774,6 @@
           <t>A+B+C+D+E+SafeF（仅当 Safe-F 通过 Future Leakage Audit）</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -790,7 +786,6 @@
           <t>中位数 / 类别水平 / 技能阈值 / SVD 只在 Temporal train 拟合</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -803,7 +798,6 @@
           <t>只用 validation MAE 选择主模型；候选含 Dummy / Ridge / RandomForest / CatBoost / LightGBM</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,7 +805,6 @@
           <t>test 纪律</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>test 仅在配置锁定后一次性评估，未据 test 调整任何配置</t>
@@ -829,7 +822,6 @@
           <t>本轮使用的全部特征列中命中爬取时间字段：无</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -842,7 +834,6 @@
           <t>本实验是当前集中采集样本内部按业务发布时间排序的**回顾性**时间划分，不是严格的历史在线滚动预测；集中抓取、存量 / 幸存样本选择都会影响结果。三种划分对应不同评估问题，不得排名谁更好。</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -855,7 +846,6 @@
           <t>Stage25 Random test MAE 35.335506；Company Group test MAE 52.049937（52.049937）</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1234,7 +1224,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阈值口径</t>
+          <t>阈值设定</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1291,7 +1281,6 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1316,7 +1305,6 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1341,7 +1329,6 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1366,12 +1353,8 @@
           <t>技能阈值</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>351</v>
       </c>
@@ -1388,9 +1371,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>367</v>
       </c>
@@ -1407,9 +1387,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>399</v>
       </c>
@@ -1697,7 +1674,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1739,8 +1716,6 @@
           <t>同一协议：A+B+C+D+E、固定 model_splits 同一 Random Split、固定 LightGBM 与 Stage25 技能阈值 / 文本维度（100 / 16），只在 random train 上拟合估计器</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1807,8 +1782,6 @@
           <t>同一协议：仅使用发布日期最早的约 70%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1838,8 +1811,6 @@
           <t>与 Stage25 正式主模型协议一致</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1869,8 +1840,6 @@
           <t>主实验为 A+B+C+D+E；本行仅作补充对照，不替代主结果；特征维度 358</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1900,8 +1869,6 @@
           <t>只读引用既有正式结果（30 号表 09）</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1931,8 +1898,6 @@
           <t>只读引用既有正式结果（31 号表 04）</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
